--- a/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
+++ b/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1649</v>
+        <v>1598</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1649呎 (3房)
+          <t>MANOR B | 1598呎 (3房)
 -
 -
 (待售)</t>

--- a/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
+++ b/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2005</v>
+        <v>2125</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>172600000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>86085</v>
+        <v>81224</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1985</v>
+        <v>2080</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>156000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>78589</v>
+        <v>75000</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1985</v>
+        <v>2080</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1985</v>
+        <v>2080</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>176000000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>88665</v>
+        <v>84615</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1985</v>
+        <v>2104</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>188000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>94710</v>
+        <v>89354</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1985</v>
+        <v>2080</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1985</v>
+        <v>2104</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1985</v>
+        <v>2080</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1985</v>
+        <v>2104</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2627</v>
+        <v>2771</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>288000000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>109631</v>
+        <v>103934</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2013</v>
+        <v>2133</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>129200000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>80000</v>
+        <v>77598</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1598</v>
+        <v>1649</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1617</v>
+        <v>1668</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4599,9 +4599,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>MANOR A | 2005呎 (4+房)
+          <t>MANOR A | 2125呎 (4+房)
 $17260万
-$86,085/呎
+$81,224/呎
 (20年-12月-08日)</t>
         </is>
       </c>
@@ -4657,9 +4657,9 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>MANOR B | 1985呎 (3房)
+          <t>MANOR B | 2080呎 (3房)
 $15600万
-$78,589/呎
+$75,000/呎
 (26年-01月-12日)</t>
         </is>
       </c>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1985呎 (4+房)
+          <t>MANOR B | 2080呎 (4+房)
 -
 -
 (待售)</t>
@@ -4857,17 +4857,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>MANOR A | 1985呎 (4+房)
+          <t>MANOR A | 2104呎 (4+房)
 $18800万
-$94,710/呎
+$89,354/呎
 (21年-01月-05日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>MANOR B | 1985呎 (4+房)
+          <t>MANOR B | 2080呎 (4+房)
 $17600万
-$88,665/呎
+$84,615/呎
 (21年-01月-05日)</t>
         </is>
       </c>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>MANOR A | 1985呎 (4+房)
+          <t>MANOR A | 2104呎 (4+房)
 -
 -
 (待售)</t>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1985呎 (4+房)
+          <t>MANOR B | 2080呎 (4+房)
 -
 -
 (待售)</t>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>MANOR A | 1985呎 (4+房)
+          <t>MANOR A | 2104呎 (4+房)
 -
 -
 (待售)</t>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1985呎 (4+房)
+          <t>MANOR B | 2080呎 (4+房)
 -
 -
 (待售)</t>
@@ -5096,9 +5096,9 @@
       <c r="C6" s="20" t="inlineStr"/>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>SKY MANOR | 2627呎 (4+房)
+          <t>SKY MANOR | 2771呎 (4+房)
 $28800万
-$109,631/呎
+$103,934/呎
 (22年-06月-15日)</t>
         </is>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>MANOR A | 2013呎 (4+房)
+          <t>MANOR A | 2133呎 (4+房)
 -
 -
 (待售)</t>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1615呎 (3房)
+          <t>MANOR B | 1665呎 (3房)
 -
 -
 (待售)</t>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>MANOR B | 1615呎 (3房)
+          <t>MANOR B | 1665呎 (3房)
 招标单位
 -
 (暂停销售)</t>
@@ -5656,9 +5656,9 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>MANOR B | 1615呎 (3房)
+          <t>MANOR B | 1665呎 (3房)
 $12920万
-$80,000/呎
+$77,598/呎
 (21年-01月-05日)</t>
         </is>
       </c>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>MANOR A | 1617呎 (3房)
+          <t>MANOR A | 1668呎 (3房)
 -
 -
 (待售)</t>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>MANOR B | 1598呎 (3房)
+          <t>MANOR B | 1649呎 (3房)
 -
 -
 (待售)</t>
